--- a/meteran_listrik.xlsx
+++ b/meteran_listrik.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Tanggal</t>
   </si>
@@ -24,24 +24,12 @@
   <si>
     <t>Angka Meteran</t>
   </si>
-  <si>
-    <t>12-05-2026</t>
-  </si>
-  <si>
-    <t>56. PANEL BMF</t>
-  </si>
-  <si>
-    <t>30. DEEPWELL 2 FISHPOND V8 X 30</t>
-  </si>
-  <si>
-    <t>57803.9</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +92,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -182,6 +175,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -216,6 +210,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -391,11 +386,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -406,28 +406,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
